--- a/data/developmental_stages_events.xlsx
+++ b/data/developmental_stages_events.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rb4174/Documents/projects/brain_dev_primates/analysis/paper_figs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://princetonu-my.sharepoint.com/personal/rb4174_princeton_edu/Documents/Projects/brain_dev_primates/altricial_brain_vocal_learning/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14FBAA80-95B2-F744-9A0F-9109F34AA1FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="108" documentId="13_ncr:1_{14FBAA80-95B2-F744-9A0F-9109F34AA1FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58A617A4-53BC-C04F-ACA2-E910478BFF4A}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17360" xr2:uid="{EB79B910-5D76-2949-8AA6-D64B7991AD5F}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{EB79B910-5D76-2949-8AA6-D64B7991AD5F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$82</definedName>
     <definedName name="capuchin_gestation">Sheet1!$F$16</definedName>
     <definedName name="chimp_gestation">Sheet1!$F$12</definedName>
+    <definedName name="gorilla_gestation">Sheet1!$D$19</definedName>
     <definedName name="human_gestation">Sheet1!$F$13</definedName>
     <definedName name="marmoset_gestation">Sheet1!$F$14</definedName>
     <definedName name="Rhesus_gestation">Sheet1!$F$15</definedName>
@@ -68,12 +69,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="104">
   <si>
     <t>event</t>
-  </si>
-  <si>
-    <t>specie</t>
   </si>
   <si>
     <t>original_format</t>
@@ -348,6 +346,42 @@
   </si>
   <si>
     <t>https://royalsocietypublishing.org/doi/full/10.1098/rsbl.2009.0773?casa_token=uJY3G7vdDzkAAAAA%3ACMjH5DirG6WFo9RHe_z1jBP7Mf-R83kWdd_YrLtvkEAo56wazbVWxJhH-NuVGa9_r4WD3rKBDasPqJc</t>
+  </si>
+  <si>
+    <t>species</t>
+  </si>
+  <si>
+    <t>Gorilla</t>
+  </si>
+  <si>
+    <t>255 days</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1002/ajpa.20474</t>
+  </si>
+  <si>
+    <t>27-51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">distribution of weaning age </t>
+  </si>
+  <si>
+    <t>https://link.springer.com/article/10.1007/s00265-016-2066-6</t>
+  </si>
+  <si>
+    <t>Juvenile/subadult</t>
+  </si>
+  <si>
+    <t>7.7 years</t>
+  </si>
+  <si>
+    <t>Breuer, https://onlinelibrary.wiley.com/doi/epdf/10.1002/ajp.20628</t>
+  </si>
+  <si>
+    <t>3.50 year</t>
+  </si>
+  <si>
+    <t>0.994 years</t>
   </si>
 </sst>
 </file>
@@ -440,7 +474,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -450,6 +484,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE4C5FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -467,7 +507,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -493,9 +533,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -513,6 +550,15 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -583,6 +629,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -882,17 +932,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85E944EE-19B2-F048-840C-8FDF46BBA4E6}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:O82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.83203125" style="8" customWidth="1"/>
     <col min="2" max="2" width="25.33203125" style="8" customWidth="1"/>
     <col min="3" max="3" width="10.1640625" style="8" customWidth="1"/>
-    <col min="4" max="4" width="12.1640625" style="10" customWidth="1"/>
-    <col min="5" max="5" width="12.5" style="10" customWidth="1"/>
-    <col min="6" max="6" width="12.1640625" style="10" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" style="10" customWidth="1"/>
-    <col min="8" max="8" width="7.1640625" style="10" customWidth="1"/>
+    <col min="4" max="4" width="12.1640625" style="9" customWidth="1"/>
+    <col min="5" max="5" width="12.5" style="9" customWidth="1"/>
+    <col min="6" max="6" width="12.1640625" style="9" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" style="9" customWidth="1"/>
+    <col min="8" max="8" width="7.1640625" style="9" customWidth="1"/>
     <col min="9" max="9" width="17.6640625" style="8" customWidth="1"/>
     <col min="10" max="10" width="32.1640625" style="8" customWidth="1"/>
     <col min="11" max="11" width="26.83203125" style="8" customWidth="1"/>
@@ -901,1147 +952,1294 @@
   <sheetData>
     <row r="1" spans="1:12" s="3" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>2</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" s="5">
         <f xml:space="preserve"> 12*Sheet3!B1 +chimp_gestation</f>
-        <v>84.142857142857139</v>
+        <v>131.65428571428572</v>
       </c>
       <c r="E2" s="5">
         <f xml:space="preserve"> 12*Sheet3!B1 +chimp_gestation</f>
-        <v>84.142857142857139</v>
+        <v>131.65428571428572</v>
       </c>
       <c r="F2" s="5">
-        <f t="shared" ref="F2:F39" si="0">(E2+D2)/2</f>
-        <v>84.142857142857139</v>
+        <f t="shared" ref="F2:F24" si="0">(E2+D2)/2</f>
+        <v>131.65428571428572</v>
       </c>
       <c r="G2" s="5">
-        <f>F2/4</f>
-        <v>21.035714285714285</v>
+        <f t="shared" ref="G2:G31" si="1">F2/4</f>
+        <v>32.91357142857143</v>
       </c>
       <c r="H2" s="5">
         <v>0</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="5">
         <f>24*Sheet3!B1 +human_gestation</f>
-        <v>141.77142857142854</v>
+        <v>320.2285714285714</v>
       </c>
       <c r="E3" s="5">
         <f>24*Sheet3!B1 +human_gestation</f>
-        <v>141.77142857142854</v>
+        <v>320.2285714285714</v>
       </c>
       <c r="F3" s="5">
         <f t="shared" si="0"/>
-        <v>141.77142857142854</v>
+        <v>320.2285714285714</v>
       </c>
       <c r="G3" s="5">
-        <f t="shared" ref="G3:G77" si="1">F3/4</f>
-        <v>35.442857142857136</v>
+        <f t="shared" si="1"/>
+        <v>80.05714285714285</v>
       </c>
       <c r="H3" s="5">
         <v>0</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="5">
         <f xml:space="preserve"> 5 + marmoset_gestation</f>
-        <v>25.714285714285715</v>
+        <v>37.542857142857144</v>
       </c>
       <c r="E4" s="5">
         <f xml:space="preserve"> 5 + marmoset_gestation</f>
-        <v>25.714285714285715</v>
+        <v>37.542857142857144</v>
       </c>
       <c r="F4" s="5">
         <f t="shared" si="0"/>
-        <v>25.714285714285715</v>
+        <v>37.542857142857144</v>
       </c>
       <c r="G4" s="5">
         <f t="shared" si="1"/>
-        <v>6.4285714285714288</v>
+        <v>9.3857142857142861</v>
       </c>
       <c r="H4" s="5">
         <v>0</v>
       </c>
       <c r="I4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="4" t="s">
-        <v>49</v>
-      </c>
       <c r="K4" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D5" s="5">
         <f xml:space="preserve"> 0.437*12*Sheet3!B1 + Rhesus_gestation</f>
-        <v>46.334914285714284</v>
+        <v>61.120628571428568</v>
       </c>
       <c r="E5" s="5">
         <f xml:space="preserve">  0.437*12*Sheet3!B1  + Rhesus_gestation</f>
-        <v>46.334914285714284</v>
+        <v>61.120628571428568</v>
       </c>
       <c r="F5" s="5">
         <f t="shared" si="0"/>
-        <v>46.334914285714284</v>
+        <v>61.120628571428568</v>
       </c>
       <c r="G5" s="5">
         <f t="shared" si="1"/>
-        <v>11.583728571428571</v>
+        <v>15.280157142857142</v>
       </c>
       <c r="H5" s="5">
         <v>0</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>83</v>
+        <v>51</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>82</v>
       </c>
       <c r="D6" s="5">
         <f xml:space="preserve"> 0.393*12*Sheet3!B1 + capuchin_gestation</f>
-        <v>42.707371428571427</v>
+        <v>40.993085714285712</v>
       </c>
       <c r="E6" s="5">
         <f xml:space="preserve">  0.393*12*Sheet3!B1  + capuchin_gestation</f>
-        <v>42.707371428571427</v>
+        <v>40.993085714285712</v>
       </c>
       <c r="F6" s="5">
-        <f t="shared" ref="F6" si="2">(E6+D6)/2</f>
-        <v>42.707371428571427</v>
+        <f t="shared" si="0"/>
+        <v>40.993085714285712</v>
       </c>
       <c r="G6" s="5">
-        <f t="shared" ref="G6" si="3">F6/4</f>
-        <v>10.676842857142857</v>
+        <f t="shared" si="1"/>
+        <v>10.248271428571428</v>
       </c>
       <c r="H6" s="5">
         <v>0</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>7</v>
+        <v>51</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>93</v>
       </c>
       <c r="D7" s="5">
-        <f xml:space="preserve"> 36*Sheet3!B1 +chimp_gestation</f>
-        <v>187.34285714285713</v>
+        <f xml:space="preserve"> 0.994*12*Sheet3!B1 + gorilla_gestation</f>
+        <v>87.718971428571422</v>
       </c>
       <c r="E7" s="5">
-        <f xml:space="preserve"> 36*Sheet3!B1 +chimp_gestation</f>
-        <v>187.34285714285713</v>
+        <f xml:space="preserve">  0.994*12*Sheet3!B1  + gorilla_gestation</f>
+        <v>87.718971428571422</v>
       </c>
       <c r="F7" s="5">
         <f t="shared" si="0"/>
-        <v>187.34285714285713</v>
+        <v>87.718971428571422</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" si="1"/>
-        <v>46.835714285714282</v>
+        <v>21.929742857142855</v>
       </c>
       <c r="H7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="5">
-        <f xml:space="preserve"> 72*Sheet3!B1 + human_gestation</f>
-        <v>348.17142857142852</v>
+        <f xml:space="preserve"> 36*Sheet3!B1 +chimp_gestation</f>
+        <v>234.85428571428571</v>
       </c>
       <c r="E8" s="5">
-        <f xml:space="preserve"> 72*Sheet3!B1 + human_gestation</f>
-        <v>348.17142857142852</v>
+        <f xml:space="preserve"> 36*Sheet3!B1 +chimp_gestation</f>
+        <v>234.85428571428571</v>
       </c>
       <c r="F8" s="5">
         <f t="shared" si="0"/>
-        <v>348.17142857142852</v>
+        <v>234.85428571428571</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" si="1"/>
-        <v>87.04285714285713</v>
+        <v>58.713571428571427</v>
       </c>
       <c r="H8" s="5">
         <v>0</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="5">
-        <f xml:space="preserve"> 3.6*Sheet3!B1 + marmoset_gestation</f>
-        <v>36.194285714285712</v>
+        <f xml:space="preserve"> 72*Sheet3!B1 + human_gestation</f>
+        <v>526.62857142857138</v>
       </c>
       <c r="E9" s="5">
-        <f xml:space="preserve"> 3.6*Sheet3!B1 + marmoset_gestation</f>
-        <v>36.194285714285712</v>
+        <f xml:space="preserve"> 72*Sheet3!B1 + human_gestation</f>
+        <v>526.62857142857138</v>
       </c>
       <c r="F9" s="5">
         <f t="shared" si="0"/>
-        <v>36.194285714285712</v>
+        <v>526.62857142857138</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="1"/>
-        <v>9.048571428571428</v>
+        <v>131.65714285714284</v>
       </c>
       <c r="H9" s="5">
         <v>0</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="D10" s="5">
-        <f xml:space="preserve">  1.35*12*Sheet3!B1  + Rhesus_gestation</f>
-        <v>93.445714285714303</v>
+        <f xml:space="preserve"> 3.6*Sheet3!B1 + marmoset_gestation</f>
+        <v>48.022857142857148</v>
       </c>
       <c r="E10" s="5">
-        <f xml:space="preserve">  1.35*12*Sheet3!B1  + Rhesus_gestation</f>
-        <v>93.445714285714303</v>
+        <f xml:space="preserve"> 3.6*Sheet3!B1 + marmoset_gestation</f>
+        <v>48.022857142857148</v>
       </c>
       <c r="F10" s="5">
         <f t="shared" si="0"/>
-        <v>93.445714285714303</v>
+        <v>48.022857142857148</v>
       </c>
       <c r="G10" s="5">
         <f t="shared" si="1"/>
-        <v>23.361428571428576</v>
+        <v>12.005714285714287</v>
       </c>
       <c r="H10" s="5">
         <v>0</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>83</v>
+        <v>52</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="D11" s="5">
-        <f xml:space="preserve">  1.15*12*Sheet3!B1  + capuchin_gestation</f>
-        <v>81.76857142857142</v>
+        <f xml:space="preserve">  1.35*12*Sheet3!B1  + Rhesus_gestation</f>
+        <v>108.23142857142858</v>
       </c>
       <c r="E11" s="5">
-        <f xml:space="preserve">  1.15*12*Sheet3!B1  + capuchin_gestation</f>
-        <v>81.76857142857142</v>
+        <f xml:space="preserve">  1.35*12*Sheet3!B1  + Rhesus_gestation</f>
+        <v>108.23142857142858</v>
       </c>
       <c r="F11" s="5">
-        <f t="shared" ref="F11" si="4">(E11+D11)/2</f>
-        <v>81.76857142857142</v>
+        <f t="shared" si="0"/>
+        <v>108.23142857142858</v>
       </c>
       <c r="G11" s="5">
-        <f t="shared" ref="G11" si="5">F11/4</f>
-        <v>20.442142857142855</v>
+        <f t="shared" si="1"/>
+        <v>27.057857142857145</v>
       </c>
       <c r="H11" s="5">
         <v>0</v>
       </c>
       <c r="I11" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K11" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>7</v>
+        <v>52</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>82</v>
       </c>
       <c r="D12" s="5">
+        <f xml:space="preserve">  1.15*12*Sheet3!B1  + capuchin_gestation</f>
+        <v>80.054285714285712</v>
+      </c>
+      <c r="E12" s="5">
+        <f xml:space="preserve">  1.15*12*Sheet3!B1  + capuchin_gestation</f>
+        <v>80.054285714285712</v>
+      </c>
+      <c r="F12" s="5">
+        <f t="shared" si="0"/>
+        <v>80.054285714285712</v>
+      </c>
+      <c r="G12" s="5">
+        <f t="shared" si="1"/>
+        <v>20.013571428571428</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" s="5">
+        <f xml:space="preserve">  3.5*12*Sheet3!B1  + gorilla_gestation</f>
+        <v>217.02857142857141</v>
+      </c>
+      <c r="E13" s="5">
+        <f xml:space="preserve">  3.5*12*Sheet3!B1  + gorilla_gestation</f>
+        <v>217.02857142857141</v>
+      </c>
+      <c r="F13" s="5">
+        <f t="shared" si="0"/>
+        <v>217.02857142857141</v>
+      </c>
+      <c r="G13" s="5">
+        <f t="shared" si="1"/>
+        <v>54.257142857142853</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="L13" s="13"/>
+    </row>
+    <row r="14" spans="1:12" s="4" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="5">
         <f xml:space="preserve"> 227.8/7</f>
         <v>32.542857142857144</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E14" s="5">
         <f xml:space="preserve"> 227.8/7</f>
         <v>32.542857142857144</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F14" s="5">
         <f t="shared" si="0"/>
         <v>32.542857142857144</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G14" s="5">
         <f t="shared" si="1"/>
         <v>8.1357142857142861</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H14" s="5">
         <v>9.18</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I14" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K14" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="J12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="5">
+    </row>
+    <row r="15" spans="1:12" s="4" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="5">
         <f>270/7</f>
         <v>38.571428571428569</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E15" s="5">
         <f>270/7</f>
         <v>38.571428571428569</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F15" s="5">
         <f t="shared" si="0"/>
         <v>38.571428571428569</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G15" s="5">
         <f t="shared" si="1"/>
         <v>9.6428571428571423</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H15" s="5">
         <v>10</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="L13" s="14"/>
-    </row>
-    <row r="14" spans="1:12" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="I15" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" s="4" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="5">
         <f xml:space="preserve"> 145/7</f>
         <v>20.714285714285715</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E16" s="5">
         <f xml:space="preserve"> 145/7</f>
         <v>20.714285714285715</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F16" s="5">
         <f t="shared" si="0"/>
         <v>20.714285714285715</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G16" s="5">
         <f t="shared" si="1"/>
         <v>5.1785714285714288</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H16" s="5">
         <v>5</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K14" s="4" t="s">
+      <c r="I16" s="4" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="J16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" s="4" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="5">
         <f>166.5/7</f>
         <v>23.785714285714285</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E17" s="5">
         <f>166.5/7</f>
         <v>23.785714285714285</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F17" s="5">
         <f t="shared" si="0"/>
         <v>23.785714285714285</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G17" s="5">
         <f t="shared" si="1"/>
         <v>5.9464285714285712</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H17" s="5">
         <v>7.4</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I17" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" s="4" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="J15" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="D18" s="5">
         <f>157/7</f>
         <v>22.428571428571427</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E18" s="5">
         <f>157/7</f>
         <v>22.428571428571427</v>
       </c>
-      <c r="F16" s="5">
-        <f t="shared" ref="F16" si="6">(E16+D16)/2</f>
-        <v>22.428571428571427</v>
-      </c>
-      <c r="G16" s="5">
-        <f t="shared" ref="G16" si="7">F16/4</f>
-        <v>5.6071428571428568</v>
-      </c>
-      <c r="H16" s="5">
-        <v>2.5</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="5">
-        <f xml:space="preserve"> 96*Sheet3!B1 +_xlfn.SINGLE( chimp_gestation)</f>
-        <v>445.3428571428571</v>
-      </c>
-      <c r="E17" s="5">
-        <f xml:space="preserve"> 96*Sheet3!B1+_xlfn.SINGLE( chimp_gestation)</f>
-        <v>445.3428571428571</v>
-      </c>
-      <c r="F17" s="5">
-        <f t="shared" si="0"/>
-        <v>445.3428571428571</v>
-      </c>
-      <c r="G17" s="5">
-        <f t="shared" si="1"/>
-        <v>111.33571428571427</v>
-      </c>
-      <c r="H17" s="5">
-        <v>0</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" s="5">
-        <f xml:space="preserve"> 144*Sheet3!B1 + human_gestation</f>
-        <v>657.77142857142849</v>
-      </c>
-      <c r="E18" s="5">
-        <f xml:space="preserve"> 144*Sheet3!B1 + human_gestation</f>
-        <v>657.77142857142849</v>
-      </c>
       <c r="F18" s="5">
         <f t="shared" si="0"/>
-        <v>657.77142857142849</v>
+        <v>22.428571428571427</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>164.44285714285712</v>
+        <v>5.6071428571428568</v>
       </c>
       <c r="H18" s="5">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" s="4" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>93</v>
       </c>
       <c r="D19" s="5">
-        <f xml:space="preserve"> 15*Sheet3!B1 + marmoset_gestation</f>
-        <v>85.214285714285722</v>
+        <f>255/7</f>
+        <v>36.428571428571431</v>
       </c>
       <c r="E19" s="5">
-        <f xml:space="preserve"> 15*Sheet3!B1 + marmoset_gestation</f>
-        <v>85.214285714285722</v>
+        <f>255/7</f>
+        <v>36.428571428571431</v>
       </c>
       <c r="F19" s="5">
         <f t="shared" si="0"/>
-        <v>85.214285714285722</v>
+        <v>36.428571428571431</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>21.303571428571431</v>
+        <v>9.1071428571428577</v>
       </c>
       <c r="H19" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" s="4" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="D20" s="5">
-        <f xml:space="preserve"> 30*Sheet3!B1 + Rhesus_gestation</f>
-        <v>152.78571428571428</v>
+        <f xml:space="preserve"> 96*Sheet3!B1 +_xlfn.SINGLE( chimp_gestation)</f>
+        <v>492.85428571428565</v>
       </c>
       <c r="E20" s="5">
-        <f xml:space="preserve"> 30*Sheet3!B1  + Rhesus_gestation</f>
-        <v>152.78571428571428</v>
+        <f xml:space="preserve"> 96*Sheet3!B1+_xlfn.SINGLE( chimp_gestation)</f>
+        <v>492.85428571428565</v>
       </c>
       <c r="F20" s="5">
         <f t="shared" si="0"/>
-        <v>152.78571428571428</v>
+        <v>492.85428571428565</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>38.196428571428569</v>
+        <v>123.21357142857141</v>
       </c>
       <c r="H20" s="5">
         <v>0</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" s="4" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>83</v>
+        <v>56</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="D21" s="5">
-        <f xml:space="preserve"> 4*12*Sheet3!B1 + capuchin_gestation</f>
-        <v>228.82857142857139</v>
+        <f xml:space="preserve"> 144*Sheet3!B1 + human_gestation</f>
+        <v>836.22857142857129</v>
       </c>
       <c r="E21" s="5">
-        <f xml:space="preserve"> 4*12*Sheet3!B1 + capuchin_gestation</f>
-        <v>228.82857142857139</v>
+        <f xml:space="preserve"> 144*Sheet3!B1 + human_gestation</f>
+        <v>836.22857142857129</v>
       </c>
       <c r="F21" s="5">
-        <f t="shared" ref="F21" si="8">(E21+D21)/2</f>
-        <v>228.82857142857139</v>
+        <f t="shared" si="0"/>
+        <v>836.22857142857129</v>
       </c>
       <c r="G21" s="5">
-        <f t="shared" ref="G21" si="9">F21/4</f>
-        <v>57.207142857142848</v>
+        <f t="shared" si="1"/>
+        <v>209.05714285714282</v>
       </c>
       <c r="H21" s="5">
         <v>0</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" s="6" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" s="6" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>7</v>
-      </c>
       <c r="D22" s="5">
-        <f xml:space="preserve"> AVERAGE(4.2,4,4.1,4)*(12*Sheet3!B1) +_xlfn.SINGLE( chimp_gestation)</f>
-        <v>242.8128571428571</v>
+        <f xml:space="preserve"> 15*Sheet3!B1 + marmoset_gestation</f>
+        <v>97.042857142857144</v>
       </c>
       <c r="E22" s="5">
-        <f xml:space="preserve"> AVERAGE(7.2,5,6,7)*(12*Sheet3!B1) +_xlfn.SINGLE( chimp_gestation)</f>
-        <v>357.62285714285707</v>
+        <f xml:space="preserve"> 15*Sheet3!B1 + marmoset_gestation</f>
+        <v>97.042857142857144</v>
       </c>
       <c r="F22" s="5">
         <f t="shared" si="0"/>
-        <v>300.2178571428571</v>
+        <v>97.042857142857144</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>75.054464285714275</v>
+        <v>24.260714285714286</v>
       </c>
       <c r="H22" s="5">
         <v>0</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="M22" s="7"/>
       <c r="N22" s="7"/>
       <c r="O22" s="7"/>
     </row>
-    <row r="23" spans="1:15" s="6" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" s="6" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="D23" s="5">
-        <f>12*Sheet3!B1 + human_gestation</f>
-        <v>90.171428571428564</v>
+        <f xml:space="preserve"> 30*Sheet3!B1 + Rhesus_gestation</f>
+        <v>167.57142857142856</v>
       </c>
       <c r="E23" s="5">
-        <f>24*Sheet3!B1 + human_gestation</f>
-        <v>141.77142857142854</v>
+        <f xml:space="preserve"> 30*Sheet3!B1  + Rhesus_gestation</f>
+        <v>167.57142857142856</v>
       </c>
       <c r="F23" s="5">
         <f t="shared" si="0"/>
-        <v>115.97142857142856</v>
+        <v>167.57142857142856</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>28.99285714285714</v>
+        <v>41.892857142857139</v>
       </c>
       <c r="H23" s="5">
         <v>0</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="M23" s="7"/>
       <c r="N23" s="7"/>
       <c r="O23" s="7"/>
     </row>
-    <row r="24" spans="1:15" s="6" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" s="6" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>5</v>
+        <v>56</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>82</v>
       </c>
       <c r="D24" s="5">
-        <f xml:space="preserve"> 12 + marmoset_gestation</f>
-        <v>32.714285714285715</v>
+        <f xml:space="preserve"> 4*12*Sheet3!B1 + capuchin_gestation</f>
+        <v>227.1142857142857</v>
       </c>
       <c r="E24" s="5">
-        <f xml:space="preserve"> 16 + marmoset_gestation</f>
-        <v>36.714285714285715</v>
+        <f xml:space="preserve"> 4*12*Sheet3!B1 + capuchin_gestation</f>
+        <v>227.1142857142857</v>
       </c>
       <c r="F24" s="5">
         <f t="shared" si="0"/>
-        <v>34.714285714285715</v>
+        <v>227.1142857142857</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="1"/>
-        <v>8.6785714285714288</v>
+        <v>56.778571428571425</v>
       </c>
       <c r="H24" s="5">
         <v>0</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>9</v>
+        <v>88</v>
       </c>
       <c r="M24" s="7"/>
       <c r="N24" s="7"/>
       <c r="O24" s="7"/>
     </row>
-    <row r="25" spans="1:15" s="6" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" s="6" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>46</v>
+        <v>56</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>93</v>
       </c>
       <c r="D25" s="5">
-        <f>10*Sheet3!B1 + Rhesus_gestation</f>
-        <v>66.785714285714278</v>
+        <f xml:space="preserve"> 7.7*12*Sheet3!B1 + gorilla_gestation</f>
+        <v>433.74857142857144</v>
       </c>
       <c r="E25" s="5">
-        <f>14*Sheet3!B1 + Rhesus_gestation</f>
-        <v>83.98571428571428</v>
+        <f xml:space="preserve"> 7.7*12*Sheet3!B1 + gorilla_gestation</f>
+        <v>433.74857142857144</v>
       </c>
       <c r="F25" s="5">
-        <f t="shared" si="0"/>
-        <v>75.385714285714272</v>
+        <f xml:space="preserve"> 7.7*12*Sheet3!B1 + gorilla_gestation</f>
+        <v>433.74857142857144</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>18.846428571428568</v>
+        <v>108.43714285714286</v>
       </c>
       <c r="H25" s="5">
         <v>0</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>20</v>
+        <v>99</v>
+      </c>
+      <c r="K25" s="17" t="s">
+        <v>101</v>
       </c>
       <c r="M25" s="7"/>
       <c r="N25" s="7"/>
       <c r="O25" s="7"/>
     </row>
-    <row r="26" spans="1:15" s="6" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" s="6" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>83</v>
+        <v>3</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="D26" s="5">
-        <f>12*Sheet3!B1 + capuchin_gestation</f>
-        <v>74.028571428571425</v>
+        <f xml:space="preserve"> AVERAGE(4.2,4,4.1,4)*(12*Sheet3!B1) +_xlfn.SINGLE( chimp_gestation)</f>
+        <v>290.32428571428568</v>
       </c>
       <c r="E26" s="5">
-        <f>12*Sheet3!B1 + capuchin_gestation</f>
-        <v>74.028571428571425</v>
+        <f xml:space="preserve"> AVERAGE(7.2,5,6,7)*(12*Sheet3!B1) +_xlfn.SINGLE( chimp_gestation)</f>
+        <v>405.13428571428562</v>
       </c>
       <c r="F26" s="5">
-        <f t="shared" ref="F26" si="10">(E26+D26)/2</f>
-        <v>74.028571428571425</v>
+        <f t="shared" ref="F26:F31" si="2">(E26+D26)/2</f>
+        <v>347.72928571428565</v>
       </c>
       <c r="G26" s="5">
-        <f t="shared" ref="G26" si="11">F26/4</f>
-        <v>18.507142857142856</v>
+        <f t="shared" si="1"/>
+        <v>86.932321428571413</v>
       </c>
       <c r="H26" s="5">
         <v>0</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="M26" s="7"/>
       <c r="N26" s="7"/>
       <c r="O26" s="7"/>
     </row>
-    <row r="27" spans="1:15" s="6" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-    </row>
-    <row r="28" spans="1:15" s="6" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="9"/>
-    </row>
-    <row r="29" spans="1:15" s="6" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="9"/>
-    </row>
-    <row r="30" spans="1:15" s="6" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-    </row>
-    <row r="31" spans="1:15" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="K31" s="11"/>
-    </row>
-    <row r="32" spans="1:15" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" s="6" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="5">
+        <f>12*Sheet3!B1 + human_gestation</f>
+        <v>268.62857142857138</v>
+      </c>
+      <c r="E27" s="5">
+        <f>24*Sheet3!B1 + human_gestation</f>
+        <v>320.2285714285714</v>
+      </c>
+      <c r="F27" s="5">
+        <f t="shared" si="2"/>
+        <v>294.42857142857139</v>
+      </c>
+      <c r="G27" s="5">
+        <f t="shared" si="1"/>
+        <v>73.607142857142847</v>
+      </c>
+      <c r="H27" s="5">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" s="6" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" s="5">
+        <f xml:space="preserve"> 12 + marmoset_gestation</f>
+        <v>44.542857142857144</v>
+      </c>
+      <c r="E28" s="5">
+        <f xml:space="preserve"> 16 + marmoset_gestation</f>
+        <v>48.542857142857144</v>
+      </c>
+      <c r="F28" s="5">
+        <f t="shared" si="2"/>
+        <v>46.542857142857144</v>
+      </c>
+      <c r="G28" s="5">
+        <f t="shared" si="1"/>
+        <v>11.635714285714286</v>
+      </c>
+      <c r="H28" s="5">
+        <v>0</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" s="6" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="5">
+        <f>10*Sheet3!B1 + Rhesus_gestation</f>
+        <v>81.571428571428569</v>
+      </c>
+      <c r="E29" s="5">
+        <f>14*Sheet3!B1 + Rhesus_gestation</f>
+        <v>98.771428571428572</v>
+      </c>
+      <c r="F29" s="5">
+        <f t="shared" si="2"/>
+        <v>90.171428571428578</v>
+      </c>
+      <c r="G29" s="5">
+        <f t="shared" si="1"/>
+        <v>22.542857142857144</v>
+      </c>
+      <c r="H29" s="5">
+        <v>0</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" s="6" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30" s="5">
+        <f>12*Sheet3!B1 + capuchin_gestation</f>
+        <v>72.314285714285717</v>
+      </c>
+      <c r="E30" s="5">
+        <f>12*Sheet3!B1 + capuchin_gestation</f>
+        <v>72.314285714285717</v>
+      </c>
+      <c r="F30" s="5">
+        <f t="shared" si="2"/>
+        <v>72.314285714285717</v>
+      </c>
+      <c r="G30" s="5">
+        <f t="shared" si="1"/>
+        <v>18.078571428571429</v>
+      </c>
+      <c r="H30" s="5">
+        <v>0</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" s="4" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D31" s="5">
+        <f>27*Sheet3!B1 + gorilla_gestation</f>
+        <v>152.52857142857141</v>
+      </c>
+      <c r="E31" s="5">
+        <f>51*Sheet3!B1 + gorilla_gestation</f>
+        <v>255.7285714285714</v>
+      </c>
+      <c r="F31" s="5">
+        <f t="shared" si="2"/>
+        <v>204.12857142857141</v>
+      </c>
+      <c r="G31" s="5">
+        <f t="shared" si="1"/>
+        <v>51.032142857142851</v>
+      </c>
+      <c r="H31" s="5">
+        <v>0</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="K31" s="17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" s="4" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
     </row>
-    <row r="33" spans="1:11" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" s="4" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
     </row>
-    <row r="34" spans="1:11" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" s="4" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
-      <c r="K34" s="11"/>
-    </row>
-    <row r="35" spans="1:11" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K34" s="10"/>
+    </row>
+    <row r="35" spans="1:11" s="4" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
-      <c r="K35" s="11"/>
-    </row>
-    <row r="36" spans="1:11" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K35" s="10"/>
+    </row>
+    <row r="36" spans="1:11" s="4" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
-      <c r="K36" s="12"/>
-    </row>
-    <row r="37" spans="1:11" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K36" s="11"/>
+    </row>
+    <row r="37" spans="1:11" s="4" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
     </row>
-    <row r="38" spans="1:11" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" s="4" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
     </row>
-    <row r="39" spans="1:11" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" s="4" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
-      <c r="K39" s="11"/>
-    </row>
-    <row r="40" spans="1:11" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K39" s="10"/>
+    </row>
+    <row r="40" spans="1:11" s="4" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
-      <c r="K40" s="11"/>
-    </row>
-    <row r="41" spans="1:11" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K40" s="10"/>
+    </row>
+    <row r="41" spans="1:11" s="4" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -2054,7 +2252,7 @@
       <c r="J41" s="6"/>
       <c r="K41" s="6"/>
     </row>
-    <row r="42" spans="1:11" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" s="4" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -2067,7 +2265,7 @@
       <c r="J42" s="6"/>
       <c r="K42" s="6"/>
     </row>
-    <row r="43" spans="1:11" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" s="4" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -2080,7 +2278,7 @@
       <c r="J43" s="6"/>
       <c r="K43" s="6"/>
     </row>
-    <row r="44" spans="1:11" s="4" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" s="4" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -2093,11 +2291,11 @@
       <c r="J44" s="6"/>
       <c r="K44" s="6"/>
     </row>
-    <row r="45" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
     </row>
-    <row r="46" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -2110,11 +2308,11 @@
       <c r="J46" s="6"/>
       <c r="K46" s="6"/>
     </row>
-    <row r="47" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
     </row>
-    <row r="48" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -2127,7 +2325,7 @@
       <c r="J48" s="6"/>
       <c r="K48" s="6"/>
     </row>
-    <row r="49" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -2140,7 +2338,7 @@
       <c r="J49" s="6"/>
       <c r="K49" s="6"/>
     </row>
-    <row r="50" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -2153,56 +2351,56 @@
       <c r="J50" s="6"/>
       <c r="K50" s="6"/>
     </row>
-    <row r="51" spans="1:11" s="6" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" s="6" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D51" s="7"/>
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
     </row>
-    <row r="52" spans="1:11" s="6" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" s="6" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D52" s="7"/>
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
     </row>
-    <row r="53" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
     </row>
-    <row r="54" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
-      <c r="K54" s="13"/>
-    </row>
-    <row r="55" spans="1:11" s="6" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K54" s="12"/>
+    </row>
+    <row r="55" spans="1:11" s="6" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
-      <c r="D55" s="10"/>
-      <c r="E55" s="10"/>
-      <c r="F55" s="10"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9"/>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="8"/>
       <c r="J55" s="8"/>
       <c r="K55" s="8"/>
     </row>
-    <row r="56" spans="1:11" s="6" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D56" s="10"/>
-      <c r="E56" s="10"/>
-      <c r="F56" s="10"/>
+    <row r="56" spans="1:11" s="6" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9"/>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
       <c r="I56" s="8"/>
       <c r="J56" s="8"/>
       <c r="K56" s="8"/>
     </row>
-    <row r="57" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -2215,15 +2413,15 @@
       <c r="J57" s="6"/>
       <c r="K57" s="6"/>
     </row>
-    <row r="58" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
     </row>
-    <row r="59" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
     </row>
-    <row r="60" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -2236,11 +2434,11 @@
       <c r="J60" s="6"/>
       <c r="K60" s="6"/>
     </row>
-    <row r="61" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
     </row>
-    <row r="62" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -2253,7 +2451,7 @@
       <c r="J62" s="6"/>
       <c r="K62" s="6"/>
     </row>
-    <row r="63" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -2266,7 +2464,7 @@
       <c r="J63" s="6"/>
       <c r="K63" s="6"/>
     </row>
-    <row r="64" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -2279,19 +2477,19 @@
       <c r="J64" s="6"/>
       <c r="K64" s="6"/>
     </row>
-    <row r="65" spans="1:15" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:15" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
-      <c r="M65" s="10"/>
-      <c r="N65" s="10"/>
-      <c r="O65" s="10"/>
-    </row>
-    <row r="66" spans="1:15" s="6" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M65" s="9"/>
+      <c r="N65" s="9"/>
+      <c r="O65" s="9"/>
+    </row>
+    <row r="66" spans="1:15" s="6" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="8"/>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
-      <c r="D66" s="10"/>
-      <c r="E66" s="10"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="9"/>
       <c r="F66" s="7"/>
       <c r="G66" s="5"/>
       <c r="H66" s="5"/>
@@ -2302,7 +2500,7 @@
       <c r="N66" s="7"/>
       <c r="O66" s="7"/>
     </row>
-    <row r="67" spans="1:15" s="6" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:15" s="6" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D67" s="7"/>
       <c r="E67" s="7"/>
       <c r="F67" s="7"/>
@@ -2312,27 +2510,27 @@
       <c r="N67" s="7"/>
       <c r="O67" s="7"/>
     </row>
-    <row r="68" spans="1:15" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:15" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
-      <c r="M68" s="10"/>
-      <c r="N68" s="10"/>
-      <c r="O68" s="10"/>
-    </row>
-    <row r="69" spans="1:15" s="6" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M68" s="9"/>
+      <c r="N68" s="9"/>
+      <c r="O68" s="9"/>
+    </row>
+    <row r="69" spans="1:15" s="6" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="8"/>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
-      <c r="D69" s="10"/>
-      <c r="E69" s="10"/>
-      <c r="F69" s="10"/>
+      <c r="D69" s="9"/>
+      <c r="E69" s="9"/>
+      <c r="F69" s="9"/>
       <c r="G69" s="5"/>
       <c r="H69" s="5"/>
       <c r="I69" s="8"/>
       <c r="J69" s="8"/>
       <c r="K69" s="8"/>
     </row>
-    <row r="70" spans="1:15" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:15" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="6"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -2345,7 +2543,7 @@
       <c r="J70" s="6"/>
       <c r="K70" s="6"/>
     </row>
-    <row r="71" spans="1:15" s="6" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:15" s="6" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D71" s="7"/>
       <c r="E71" s="7"/>
       <c r="F71" s="7"/>
@@ -2355,27 +2553,27 @@
       <c r="N71" s="7"/>
       <c r="O71" s="7"/>
     </row>
-    <row r="72" spans="1:15" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:15" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
-      <c r="M72" s="10"/>
-      <c r="N72" s="10"/>
-      <c r="O72" s="10"/>
-    </row>
-    <row r="73" spans="1:15" s="6" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M72" s="9"/>
+      <c r="N72" s="9"/>
+      <c r="O72" s="9"/>
+    </row>
+    <row r="73" spans="1:15" s="6" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="8"/>
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
-      <c r="D73" s="10"/>
-      <c r="E73" s="10"/>
-      <c r="F73" s="10"/>
+      <c r="D73" s="9"/>
+      <c r="E73" s="9"/>
+      <c r="F73" s="9"/>
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
       <c r="I73" s="8"/>
       <c r="J73" s="8"/>
       <c r="K73" s="8"/>
     </row>
-    <row r="74" spans="1:15" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:15" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
@@ -2388,38 +2586,38 @@
       <c r="J74" s="6"/>
       <c r="K74" s="6"/>
     </row>
-    <row r="75" spans="1:15" s="6" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:15" s="6" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="8"/>
       <c r="B75" s="8"/>
       <c r="C75" s="8"/>
-      <c r="D75" s="10"/>
-      <c r="E75" s="10"/>
-      <c r="F75" s="10"/>
+      <c r="D75" s="9"/>
+      <c r="E75" s="9"/>
+      <c r="F75" s="9"/>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
       <c r="I75" s="8"/>
       <c r="J75" s="8"/>
       <c r="K75" s="8"/>
     </row>
-    <row r="76" spans="1:15" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:15" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G76" s="5"/>
       <c r="H76" s="5"/>
     </row>
-    <row r="77" spans="1:15" s="6" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:15" s="6" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D77" s="7"/>
       <c r="E77" s="7"/>
       <c r="F77" s="7"/>
       <c r="G77" s="5"/>
       <c r="H77" s="5"/>
     </row>
-    <row r="78" spans="1:15" s="6" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:15" s="6" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D78" s="7"/>
       <c r="E78" s="7"/>
       <c r="F78" s="7"/>
       <c r="G78" s="5"/>
       <c r="H78" s="5"/>
     </row>
-    <row r="79" spans="1:15" s="6" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:15" s="6" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="8"/>
       <c r="D79" s="7"/>
       <c r="E79" s="7"/>
@@ -2429,7 +2627,7 @@
       <c r="J79" s="8"/>
       <c r="K79" s="8"/>
     </row>
-    <row r="80" spans="1:15" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:15" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
       <c r="D80" s="7"/>
@@ -2439,34 +2637,40 @@
       <c r="H80" s="5"/>
       <c r="I80" s="6"/>
     </row>
-    <row r="81" spans="1:11" s="6" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" s="6" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="8"/>
       <c r="B81" s="8"/>
-      <c r="D81" s="10"/>
-      <c r="E81" s="10"/>
-      <c r="F81" s="10"/>
-      <c r="G81" s="10"/>
-      <c r="H81" s="10"/>
+      <c r="D81" s="9"/>
+      <c r="E81" s="9"/>
+      <c r="F81" s="9"/>
+      <c r="G81" s="9"/>
+      <c r="H81" s="9"/>
       <c r="I81" s="8"/>
       <c r="J81" s="8"/>
       <c r="K81" s="8"/>
     </row>
-    <row r="82" spans="1:11" s="6" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11" s="6" customFormat="1" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="8"/>
       <c r="B82" s="8"/>
-      <c r="D82" s="10"/>
-      <c r="E82" s="10"/>
-      <c r="F82" s="10"/>
-      <c r="G82" s="10"/>
-      <c r="H82" s="10"/>
+      <c r="D82" s="9"/>
+      <c r="E82" s="9"/>
+      <c r="F82" s="9"/>
+      <c r="G82" s="9"/>
+      <c r="H82" s="9"/>
       <c r="I82" s="8"/>
       <c r="J82" s="8"/>
       <c r="K82" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K82" xr:uid="{85E944EE-19B2-F048-840C-8FDF46BBA4E6}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K80">
-      <sortCondition ref="A1:A80"/>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="dental_early_infancy_ends"/>
+        <filter val="dental_late_infancy_ends"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K82">
+      <sortCondition ref="B1:B82"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -2489,8 +2693,16 @@
       <formula>"Chimpanzee"</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="K19" r:id="rId1" xr:uid="{6C96D121-96DA-7E4C-BD4D-F559157C63FD}"/>
+    <hyperlink ref="K31" r:id="rId2" xr:uid="{B890BC79-5E63-7746-BEB0-7D4295540413}"/>
+    <hyperlink ref="K25" r:id="rId3" display="https://onlinelibrary.wiley.com/doi/epdf/10.1002/ajp.20628" xr:uid="{19753D7D-09E8-F64B-941D-445A63B4EA4D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <ignoredErrors>
+    <ignoredError sqref="F25" formula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -2508,10 +2720,10 @@
   <sheetData>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="135" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" s="1">
         <v>30.428571428571427</v>
@@ -2523,21 +2735,21 @@
         <v>31.761904761904763</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="H2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1">
         <v>134.57142857142856</v>
@@ -2549,21 +2761,21 @@
         <v>134.57142857142856</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C4" s="1">
         <v>43.571428571428569</v>
@@ -2575,21 +2787,21 @@
         <v>43.571428571428569</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1">
         <v>82.714285714285722</v>
@@ -2601,245 +2813,245 @@
         <v>82.714285714285722</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="1" customFormat="1" ht="90" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="1">
         <f xml:space="preserve"> 40 + marmoset_gestation</f>
-        <v>60.714285714285715</v>
+        <v>72.542857142857144</v>
       </c>
       <c r="D6" s="1">
         <f xml:space="preserve"> 48 + marmoset_gestation</f>
-        <v>68.714285714285722</v>
+        <v>80.542857142857144</v>
       </c>
       <c r="E6" s="1">
         <f>(D6+C6*2)/3</f>
-        <v>63.380952380952387</v>
+        <v>75.209523809523816</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="2">
         <f xml:space="preserve"> 576 + human_gestation</f>
-        <v>614.57142857142856</v>
+        <v>793.02857142857147</v>
       </c>
       <c r="D7" s="2">
         <f xml:space="preserve"> 576 + human_gestation</f>
-        <v>614.57142857142856</v>
+        <v>793.02857142857147</v>
       </c>
       <c r="E7" s="2">
         <f>(D7+C7)/2</f>
-        <v>614.57142857142856</v>
+        <v>793.02857142857147</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" s="2" cm="1">
         <f t="array" ref="C8" xml:space="preserve"> 153.6 + Rhesus_gestation</f>
-        <v>177.38571428571427</v>
+        <v>192.17142857142858</v>
       </c>
       <c r="D8" s="2" cm="1">
         <f t="array" ref="D8" xml:space="preserve"> 153.6 + Rhesus_gestation</f>
-        <v>177.38571428571427</v>
+        <v>192.17142857142858</v>
       </c>
       <c r="E8" s="2">
         <f>(D8+C8)/2</f>
-        <v>177.38571428571427</v>
+        <v>192.17142857142858</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" s="2">
         <f xml:space="preserve"> 384 +_xlfn.SINGLE( chimp_gestation)</f>
-        <v>416.54285714285714</v>
+        <v>464.0542857142857</v>
       </c>
       <c r="D9" s="2">
         <f xml:space="preserve"> 384 +_xlfn.SINGLE( chimp_gestation)</f>
-        <v>416.54285714285714</v>
+        <v>464.0542857142857</v>
       </c>
       <c r="E9" s="2">
         <f>(D9+C9)/2</f>
-        <v>416.54285714285714</v>
+        <v>464.0542857142857</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="1" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" s="2">
         <f xml:space="preserve"> 22 + marmoset_gestation</f>
-        <v>42.714285714285715</v>
+        <v>54.542857142857144</v>
       </c>
       <c r="D12" s="2">
         <f xml:space="preserve"> 28 + marmoset_gestation</f>
-        <v>48.714285714285715</v>
+        <v>60.542857142857144</v>
       </c>
       <c r="E12" s="2">
         <f>(D12+C12 + (24 + marmoset_gestation))/3</f>
-        <v>45.38095238095238</v>
+        <v>57.209523809523809</v>
       </c>
       <c r="F12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="H12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="1" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" s="2">
         <f xml:space="preserve"> 288 + human_gestation</f>
-        <v>326.57142857142856</v>
+        <v>505.02857142857141</v>
       </c>
       <c r="D13" s="2">
         <f xml:space="preserve"> 288 + human_gestation</f>
-        <v>326.57142857142856</v>
+        <v>505.02857142857141</v>
       </c>
       <c r="E13" s="2">
         <f>(D13+C13)/2</f>
-        <v>326.57142857142856</v>
+        <v>505.02857142857141</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="1" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C14" s="2" cm="1">
         <f t="array" ref="C14" xml:space="preserve"> 62.4 + Rhesus_gestation</f>
-        <v>86.185714285714283</v>
+        <v>100.97142857142856</v>
       </c>
       <c r="D14" s="2" cm="1">
         <f t="array" ref="D14" xml:space="preserve"> 62.4 + Rhesus_gestation</f>
-        <v>86.185714285714283</v>
+        <v>100.97142857142856</v>
       </c>
       <c r="E14" s="2">
         <f>(D14+C14)/2</f>
-        <v>86.185714285714283</v>
+        <v>100.97142857142856</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="1" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15" s="2">
         <f xml:space="preserve"> 144 +_xlfn.SINGLE( chimp_gestation)</f>
-        <v>176.54285714285714</v>
+        <v>224.0542857142857</v>
       </c>
       <c r="D15" s="2">
         <f xml:space="preserve"> 144 +_xlfn.SINGLE( chimp_gestation)</f>
-        <v>176.54285714285714</v>
+        <v>224.0542857142857</v>
       </c>
       <c r="E15" s="2">
         <f>(D15+C15)/2</f>
-        <v>176.54285714285714</v>
+        <v>224.0542857142857</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -2857,7 +3069,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B1">
         <v>4.3</v>
